--- a/tool/package-generator/clients/package_definition_サンプル.xlsx
+++ b/tool/package-generator/clients/package_definition_サンプル.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15465498-5ECA-4F28-894E-4759CFA8A41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F554F9-9D82-4E9B-9F1D-DA53B40ABA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -572,26 +572,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -786,26 +766,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -822,4 +803,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/package_definition_サンプル.xlsx
+++ b/tool/package-generator/clients/package_definition_サンプル.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F554F9-9D82-4E9B-9F1D-DA53B40ABA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022FD26F-5760-4079-BF54-3944B2E07C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -94,6 +94,9 @@
   <si>
     <t>.\サンプルフォルダ2</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>.\サンプルフォルダA</t>
   </si>
 </sst>
 </file>
@@ -451,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -479,6 +482,14 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -572,6 +583,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -766,27 +797,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -803,23 +833,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/package_definition_サンプル.xlsx
+++ b/tool/package-generator/clients/package_definition_サンプル.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022FD26F-5760-4079-BF54-3944B2E07C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6140C1-286C-48B0-A45E-0CF420623C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>.\サンプルフォルダA</t>
+  </si>
+  <si>
+    <t>.\サンプルフォルダA\フォルダB</t>
+  </si>
+  <si>
+    <t>.\サンプルフォルダA\フォルダB\サンプルファイルC.txt</t>
   </si>
 </sst>
 </file>
@@ -454,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -491,6 +497,22 @@
       </c>
       <c r="B4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/tool/package-generator/clients/package_definition_サンプル.xlsx
+++ b/tool/package-generator/clients/package_definition_サンプル.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6140C1-286C-48B0-A45E-0CF420623C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA896AEB-4A7C-4277-862E-E867B61E2B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
     <sheet name="コースA" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テンプレート!$A$1:$C$155</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="174">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -103,6 +106,484 @@
   </si>
   <si>
     <t>.\サンプルフォルダA\フォルダB\サンプルファイルC.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\.gitignore</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\all.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\build-gui.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\check-and-post-alert.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\collect-app-data.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\create-app-data.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\kintoneデータ集計ツール.exe</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\setting-starter-auto.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\starter-auto.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\starter-manual.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\build-gui.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\check-alert.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\check-alert.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\collect-app-data.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\collect-app-data.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\collect-data-defs.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\common-env.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\create-app-data.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\create-daily-report.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\create-pulse-survey.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\excel-clean.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\gui.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\message.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\post-alert-result.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\post-alert-result.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\recovery-check-alert.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\.vscode</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\.vscode\settings.json</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\common.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\excel-com.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\file-array-io.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\gui-common.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\gui-widgets.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\kintone-rest-api.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\report-data.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\bats\library\worker-simpleLog.ps1</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\clients</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\clients\地域共催.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\clients\地域共催.xlsx</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\clients\template</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\clients\template\client.bat</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\clients\template\client.xlsx</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\check-alert-地域共催-2026-09-16_20260916_181709.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\check-alert-地域共催-2026-09-17_20260917_161450.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-02_20260916_181737.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-03_20260916_181805.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-04_20260916_181831.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-05_20260916_181913.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-06_20260916_181950.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-07_20260916_182028.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-08_20260916_182108.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-09_20260916_182145.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-10_20260916_182223.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-11_20260916_182312.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-12_20260916_182403.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-13_20260916_182450.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-16_20260916_181707.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\collect-app-data-地域共催-2026-09-17_20260917_161447.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-02_20260916_181716.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-03_20260916_181744.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-04_20260916_181811.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-05_20260916_181838.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-06_20260916_181921.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-07_20260916_181957.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-08_20260916_182036.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-09_20260916_182115.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-10_20260916_182152.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-11_20260916_182230.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-12_20260916_182321.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-daily-report-地域共催-2026-09-13_20260916_182414.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-02_20260916_181727.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-03_20260916_181755.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-04_20260916_181821.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-05_20260916_181850.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-06_20260916_181933.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-07_20260916_182015.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-08_20260916_182050.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-09_20260916_182128.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-10_20260916_182208.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-11_20260916_182251.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-12_20260916_182339.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\create-pulse-survey-地域共催-2026-09-13_20260916_182435.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\post-alert-result-地域共催-2026-09-16_20260916_182602.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\logs\post-alert-result-地域共催-2026-09-17_20260917_161548.log</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-01</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-01\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-01\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-02</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-02\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-02\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-03</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-03\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-03\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-04</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-04\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-04\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-05</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-05\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-05\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-06</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-06\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-06\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-07</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-07\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-07\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-08</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-08\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-08\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-09</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-09\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-09\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-10</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-10\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-10\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-11</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-11\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-11\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-12</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-12\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-12\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-13</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-13\地域共催-パルスサーベイ.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\01_提出状況\2026-09-13\地域共催-業務日誌.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-01.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-02.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-03.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-04.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-05.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-06.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-07.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-08.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-09.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-10.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-11.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-12.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\02_アプリデータ集計\地域共催-2026-09-13.txt</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\03_アラート検知結果</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\03_アラート検知結果\地域共催.xlsx</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\03_アラート検知結果\backup</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\03_アラート検知結果\backup\地域共催-2026-09-01.xlsx</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\03_アラート検知結果\backup\地域共催-2026-09-16.xlsx</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\output\03_アラート検知結果\backup\地域共催-2026-09-17.xlsx</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\template</t>
+  </si>
+  <si>
+    <t>.\kintone-aggregator\template\アラート検知.xlsx</t>
+  </si>
+  <si>
+    <t>拡張子</t>
+    <rPh sb="0" eb="3">
+      <t>カクチョウシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>bat</t>
+  </si>
+  <si>
+    <t>exe</t>
+  </si>
+  <si>
+    <t>ps1</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>xlsx</t>
+  </si>
+  <si>
+    <t>log</t>
+  </si>
+  <si>
+    <t>gitignore</t>
   </si>
 </sst>
 </file>
@@ -154,7 +635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -162,11 +643,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -178,6 +674,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -460,62 +959,1643 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.69921875" customWidth="1"/>
+    <col min="2" max="2" width="69" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>87</v>
+      </c>
+      <c r="C74" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>88</v>
+      </c>
+      <c r="C75" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>91</v>
+      </c>
+      <c r="C78" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>92</v>
+      </c>
+      <c r="C79" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>95</v>
+      </c>
+      <c r="C82" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C85" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C86" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>100</v>
+      </c>
+      <c r="C87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>103</v>
+      </c>
+      <c r="C90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>105</v>
+      </c>
+      <c r="C92" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>109</v>
+      </c>
+      <c r="C96" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>111</v>
+      </c>
+      <c r="C98" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>112</v>
+      </c>
+      <c r="C99" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>114</v>
+      </c>
+      <c r="C101" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>115</v>
+      </c>
+      <c r="C102" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>117</v>
+      </c>
+      <c r="C104" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>118</v>
+      </c>
+      <c r="C105" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>121</v>
+      </c>
+      <c r="C108" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>123</v>
+      </c>
+      <c r="C110" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>124</v>
+      </c>
+      <c r="C111" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>126</v>
+      </c>
+      <c r="C113" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>127</v>
+      </c>
+      <c r="C114" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>129</v>
+      </c>
+      <c r="C116" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>130</v>
+      </c>
+      <c r="C117" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>133</v>
+      </c>
+      <c r="C120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>135</v>
+      </c>
+      <c r="C122" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>136</v>
+      </c>
+      <c r="C123" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>138</v>
+      </c>
+      <c r="C125" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>139</v>
+      </c>
+      <c r="C126" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>141</v>
+      </c>
+      <c r="C128" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>142</v>
+      </c>
+      <c r="C129" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>144</v>
+      </c>
+      <c r="C131" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>145</v>
+      </c>
+      <c r="C132" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>146</v>
+      </c>
+      <c r="C133" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>148</v>
+      </c>
+      <c r="C135" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>149</v>
+      </c>
+      <c r="C136" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>150</v>
+      </c>
+      <c r="C137" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>151</v>
+      </c>
+      <c r="C138" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>152</v>
+      </c>
+      <c r="C139" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>153</v>
+      </c>
+      <c r="C140" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>154</v>
+      </c>
+      <c r="C141" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>155</v>
+      </c>
+      <c r="C142" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>156</v>
+      </c>
+      <c r="C143" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>158</v>
+      </c>
+      <c r="C145" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>160</v>
+      </c>
+      <c r="C147" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>161</v>
+      </c>
+      <c r="C148" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>162</v>
+      </c>
+      <c r="C149" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>164</v>
+      </c>
+      <c r="C151" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C155" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -523,7 +2603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75150BA2-5956-4186-B987-ACE3C5F8C674}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -596,6 +2676,14 @@
       </c>
       <c r="E7" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/tool/package-generator/clients/package_definition_サンプル.xlsx
+++ b/tool/package-generator/clients/package_definition_サンプル.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9EE37C-99F0-4B60-95F6-598939879A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB31204C-ED5D-4997-99ED-673C65607E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tool/package-generator/clients/package_definition_サンプル.xlsx
+++ b/tool/package-generator/clients/package_definition_サンプル.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB31204C-ED5D-4997-99ED-673C65607E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAE7DAA-2C2F-45EC-8645-B5D6297FDFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
